--- a/Aula14/Base_BANCO_TABAJARA.xlsx
+++ b/Aula14/Base_BANCO_TABAJARA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>nome_cliente</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>Salario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paula Tejano </t>
   </si>
 </sst>
 </file>
@@ -64,7 +67,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -96,10 +99,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -412,18 +418,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -443,63 +449,83 @@
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>12345</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>0</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>400</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>9876</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>1</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>401</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>9090909909099</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>2</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>402</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3">
+        <v>454545454545454</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3">
+        <v>403</v>
+      </c>
+      <c r="F5" s="3">
         <v>0</v>
       </c>
     </row>
